--- a/resources/table/object.xlsx
+++ b/resources/table/object.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cshyeon\fb\resources\table\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9541EA46-658F-4B9A-B378-7661D4D297A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{457F1538-5EC8-434F-921A-660E8B3C64DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17790" activeTab="1" xr2:uid="{21E5F79A-8B4E-4954-B92A-70C4053AB7E6}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{21E5F79A-8B4E-4954-B92A-70C4053AB7E6}"/>
   </bookViews>
   <sheets>
     <sheet name="object" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="20">
   <si>
     <t>uint</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -86,7 +86,16 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>system_session</t>
+    <t>id</t>
+  </si>
+  <si>
+    <t>*uint</t>
+  </si>
+  <si>
+    <t>server</t>
+  </si>
+  <si>
+    <t>system</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -486,45 +495,55 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCD16D76-AF8F-4080-85CD-ADCD2367D9FF}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="6" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>1</v>
       </c>
     </row>
@@ -537,62 +556,66 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1465B806-7697-4617-8245-9A2A79408B97}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="E4" s="1" t="s">
         <v>0</v>
       </c>
@@ -600,15 +623,18 @@
         <v>0</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I4" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>1</v>
@@ -631,22 +657,25 @@
       <c r="H5" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>15</v>
+      <c r="I5" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
+        <v>19</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -655,6 +684,9 @@
         <v>0</v>
       </c>
       <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
         <v>0</v>
       </c>
     </row>

--- a/resources/table/object.xlsx
+++ b/resources/table/object.xlsx
@@ -1,140 +1,50 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\fb\resources\table\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{457F1538-5EC8-434F-921A-660E8B3C64DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{21E5F79A-8B4E-4954-B92A-70C4053AB7E6}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="object" sheetId="1" r:id="rId1"/>
-    <sheet name="life" sheetId="5" r:id="rId2"/>
+    <sheet name="object" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="life" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="181029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="20">
-  <si>
-    <t>uint</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>server</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>uint16_t</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>color</t>
-  </si>
-  <si>
-    <t>uint8_t</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>defensive_physical</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>defensive_magical</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>based:object</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hp</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mp</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>exp</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>look</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>*uint</t>
-  </si>
-  <si>
-    <t>server</t>
-  </si>
-  <si>
-    <t>system</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="2"/>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -150,31 +60,91 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -494,205 +464,300 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCD16D76-AF8F-4080-85CD-ADCD2367D9FF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="9" style="1"/>
+    <col width="9" customWidth="1" style="1" min="1" max="1"/>
+    <col width="6" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
+    <col width="7.375" bestFit="1" customWidth="1" style="1" min="3" max="3"/>
+    <col width="6.5" bestFit="1" customWidth="1" style="1" min="4" max="4"/>
+    <col width="9" customWidth="1" style="1" min="5" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>5</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>look</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>color</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>6</v>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>*uint</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>uint16_t</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>uint8_t</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>1</v>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1465B806-7697-4617-8245-9A2A79408B97}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.375" bestFit="1" customWidth="1"/>
+    <col width="11" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
+    <col width="13" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
+    <col width="6" bestFit="1" customWidth="1" style="1" min="3" max="3"/>
+    <col width="7.375" bestFit="1" customWidth="1" style="1" min="4" max="4"/>
+    <col width="6.5" bestFit="1" customWidth="1" style="1" min="5" max="5"/>
+    <col width="6" bestFit="1" customWidth="1" style="2" min="6" max="8"/>
+    <col width="15.625" bestFit="1" customWidth="1" style="2" min="9" max="9"/>
+    <col width="15.375" bestFit="1" customWidth="1" style="2" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>10</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>based:object</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>9</v>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>look</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>color</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>mp</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>exp</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>defensive_physical</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>defensive_magical</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="1" t="s">
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>*uint</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>uint16_t</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>uint8_t</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>ulong</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>ulong</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>ulong</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="H5" s="1" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+      <c r="I5" s="1" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G6" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6">
+      <c r="H6" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
+      <c r="I6" s="0" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>